--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
   <si>
     <t/>
   </si>
   <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
+    <t>20135615</t>
+  </si>
+  <si>
+    <t>CAT CHOIZE+T&amp;S 1.2KG</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -28,280 +28,217 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20103297</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP200</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20131083</t>
+  </si>
+  <si>
+    <t>LARISST CLK LIME 370</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20083529</t>
-  </si>
-  <si>
-    <t>HAPPY TOS SEAWEED 52</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20003395</t>
+  </si>
+  <si>
+    <t>JHNSN H&amp;B MLK+RC 400</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>20026207</t>
+  </si>
+  <si>
+    <t>CIPTADENT MX.COM 190</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20130447</t>
+  </si>
+  <si>
+    <t>TOS TOS TRTCS RC140</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20087713</t>
-  </si>
-  <si>
-    <t>IDM NDL AYM PDS 90G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
-  </si>
-  <si>
-    <t>20012573</t>
-  </si>
-  <si>
-    <t>FRESTEA TEH MLATI500</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20036765</t>
-  </si>
-  <si>
-    <t>FRESTEA GRN MADU 500</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>20051344</t>
+  </si>
+  <si>
+    <t>FITBAR CHOCOLATE 20G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20004032</t>
+  </si>
+  <si>
+    <t>IDM CHOCO MEISES 80G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
+    <t>20138030</t>
+  </si>
+  <si>
+    <t>JGOAN/N LOLY LDH WRN</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20124899</t>
-  </si>
-  <si>
-    <t>CHI/FRST LYC/FZY 480</t>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20128561</t>
+  </si>
+  <si>
+    <t>IDM CCNT WTR ORGE250</t>
+  </si>
+  <si>
+    <t>10008887</t>
+  </si>
+  <si>
+    <t>ULTRA KCNG HIJAU 250</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20124898</t>
-  </si>
-  <si>
-    <t>CHI/FRST WHT/PCH 480</t>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>10036647</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT CHO1L</t>
-  </si>
-  <si>
-    <t>10000405</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT PLN1L</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
-  </si>
-  <si>
-    <t>10000107</t>
-  </si>
-  <si>
-    <t>GREEN SAND ORGNL 330</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
-  </si>
-  <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
-  </si>
-  <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>20138376</t>
-  </si>
-  <si>
-    <t>BEBELAC 1 UHT 105ML</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
+    <t>20099679</t>
+  </si>
+  <si>
+    <t>LEMONILO MIE GRG 65G</t>
+  </si>
+  <si>
+    <t>20113972</t>
+  </si>
+  <si>
+    <t>LEMONILO PDS KOREA68</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>20009269</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 135</t>
+  </si>
+  <si>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200G</t>
+  </si>
+  <si>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
+  </si>
+  <si>
+    <t>20052391</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE K/S CUP81</t>
+  </si>
+  <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
+  </si>
+  <si>
+    <t>20099297</t>
+  </si>
+  <si>
+    <t>SDAAP MIE SP.CHKN 81</t>
+  </si>
+  <si>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
+  </si>
+  <si>
+    <t>10014293</t>
+  </si>
+  <si>
+    <t>POP MIE SOTO AYM 75G</t>
+  </si>
+  <si>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
   </si>
 </sst>
 </file>
@@ -694,15 +631,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -762,15 +698,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -779,10 +715,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -802,15 +738,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -822,7 +758,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -859,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>21</v>
@@ -882,15 +818,15 @@
         <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -899,18 +835,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -919,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>21</v>
@@ -927,142 +863,142 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1076,21 +1012,21 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1102,15 +1038,15 @@
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1122,15 +1058,15 @@
         <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1139,18 +1075,18 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1162,15 +1098,15 @@
         <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1179,90 +1115,90 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1276,233 +1212,53 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="95">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135615</t>
-  </si>
-  <si>
-    <t>CAT CHOIZE+T&amp;S 1.2KG</t>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600ML</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -28,217 +28,274 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20080088</t>
+  </si>
+  <si>
+    <t>POKKA GREEN TEA 450</t>
+  </si>
+  <si>
+    <t>20138841</t>
+  </si>
+  <si>
+    <t>POKKA NAT. H.ORG 350</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20124713</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 220</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20131083</t>
-  </si>
-  <si>
-    <t>LARISST CLK LIME 370</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20003395</t>
-  </si>
-  <si>
-    <t>JHNSN H&amp;B MLK+RC 400</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20026207</t>
-  </si>
-  <si>
-    <t>CIPTADENT MX.COM 190</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20130447</t>
-  </si>
-  <si>
-    <t>TOS TOS TRTCS RC140</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>20051344</t>
-  </si>
-  <si>
-    <t>FITBAR CHOCOLATE 20G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20004032</t>
-  </si>
-  <si>
-    <t>IDM CHOCO MEISES 80G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20138030</t>
-  </si>
-  <si>
-    <t>JGOAN/N LOLY LDH WRN</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20128561</t>
-  </si>
-  <si>
-    <t>IDM CCNT WTR ORGE250</t>
-  </si>
-  <si>
-    <t>10008887</t>
-  </si>
-  <si>
-    <t>ULTRA KCNG HIJAU 250</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20103178</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LSO 330</t>
+  </si>
+  <si>
+    <t>20046319</t>
+  </si>
+  <si>
+    <t>PANDA GRASS JELY310</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20099679</t>
-  </si>
-  <si>
-    <t>LEMONILO MIE GRG 65G</t>
-  </si>
-  <si>
-    <t>20113972</t>
-  </si>
-  <si>
-    <t>LEMONILO PDS KOREA68</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>20009269</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 135</t>
-  </si>
-  <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200G</t>
-  </si>
-  <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
-  </si>
-  <si>
-    <t>20052391</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE K/S CUP81</t>
-  </si>
-  <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
-  </si>
-  <si>
-    <t>20099297</t>
-  </si>
-  <si>
-    <t>SDAAP MIE SP.CHKN 81</t>
-  </si>
-  <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10028190</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS KLG 250</t>
+  </si>
+  <si>
+    <t>20052734</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS MLN 250</t>
+  </si>
+  <si>
+    <t>20135975</t>
+  </si>
+  <si>
+    <t>OLATTE STRWB KLG 240</t>
+  </si>
+  <si>
+    <t>20089806</t>
+  </si>
+  <si>
+    <t>OLATTE PEAR KLG 240</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20136817</t>
+  </si>
+  <si>
+    <t>INDOMLK KID BNANA115</t>
+  </si>
+  <si>
+    <t>10004779</t>
+  </si>
+  <si>
+    <t>INDOMILK KID CKL 115</t>
+  </si>
+  <si>
+    <t>10004780</t>
+  </si>
+  <si>
+    <t>INDOMILK KID STRW115</t>
+  </si>
+  <si>
+    <t>10004778</t>
+  </si>
+  <si>
+    <t>INDOMILK KID VNL 115</t>
+  </si>
+  <si>
+    <t>10034797</t>
+  </si>
+  <si>
+    <t>F/FLAG CHOCO TPK 110</t>
+  </si>
+  <si>
+    <t>20096322</t>
+  </si>
+  <si>
+    <t>FF SS CAIR PLAIN 110</t>
+  </si>
+  <si>
+    <t>20038425</t>
+  </si>
+  <si>
+    <t>NTRIVE/B BLCKRNT 100</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20071510</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL LYCH 100</t>
+  </si>
+  <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
+  </si>
+  <si>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10036647</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT CHO1L</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
   </si>
   <si>
     <t>10014293</t>
   </si>
   <si>
     <t>POP MIE SOTO AYM 75G</t>
-  </si>
-  <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
   </si>
 </sst>
 </file>
@@ -631,14 +688,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -698,15 +756,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -715,7 +773,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -723,19 +781,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -743,10 +801,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -755,18 +813,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -775,18 +833,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -795,18 +853,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -815,18 +873,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -835,18 +893,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -855,30 +913,30 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -892,13 +950,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,13 +970,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -932,13 +990,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -952,10 +1010,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>43</v>
@@ -972,13 +1030,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -992,73 +1050,73 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1072,13 +1130,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1092,10 +1150,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1112,13 +1170,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1132,13 +1190,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1152,13 +1210,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1172,13 +1230,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,73 +1250,233 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>26</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -19,7 +19,7 @@
     <t>20090527</t>
   </si>
   <si>
-    <t>CRYSTALIN BTL 600ML</t>
+    <t>CRYSTALIN BTL 600mL</t>
   </si>
   <si>
     <t>EG2B</t>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="93">
   <si>
     <t/>
   </si>
@@ -31,190 +31,178 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20080088</t>
-  </si>
-  <si>
-    <t>POKKA GREEN TEA 450</t>
-  </si>
-  <si>
-    <t>20138841</t>
-  </si>
-  <si>
-    <t>POKKA NAT. H.ORG 350</t>
+    <t>20134246</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 350ML</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>20132840</t>
+  </si>
+  <si>
+    <t>IDM TEH BLCKCRRNT350</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20124713</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 220</t>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 250</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 250</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20046319</t>
-  </si>
-  <si>
-    <t>PANDA GRASS JELY310</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>10028190</t>
-  </si>
-  <si>
-    <t>LOTTE MILKIS KLG 250</t>
-  </si>
-  <si>
-    <t>20052734</t>
-  </si>
-  <si>
-    <t>LOTTE MILKIS MLN 250</t>
-  </si>
-  <si>
-    <t>20135975</t>
-  </si>
-  <si>
-    <t>OLATTE STRWB KLG 240</t>
-  </si>
-  <si>
-    <t>20089806</t>
-  </si>
-  <si>
-    <t>OLATTE PEAR KLG 240</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20136817</t>
-  </si>
-  <si>
-    <t>INDOMLK KID BNANA115</t>
-  </si>
-  <si>
-    <t>10004779</t>
-  </si>
-  <si>
-    <t>INDOMILK KID CKL 115</t>
-  </si>
-  <si>
-    <t>10004780</t>
-  </si>
-  <si>
-    <t>INDOMILK KID STRW115</t>
-  </si>
-  <si>
-    <t>10004778</t>
-  </si>
-  <si>
-    <t>INDOMILK KID VNL 115</t>
-  </si>
-  <si>
-    <t>10034797</t>
-  </si>
-  <si>
-    <t>F/FLAG CHOCO TPK 110</t>
-  </si>
-  <si>
-    <t>20096322</t>
-  </si>
-  <si>
-    <t>FF SS CAIR PLAIN 110</t>
+    <t>20138893</t>
+  </si>
+  <si>
+    <t>AMO DRMY STRAW 180ML</t>
+  </si>
+  <si>
+    <t>20138894</t>
+  </si>
+  <si>
+    <t>AMO FIZZY EASY 180ML</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>20138252</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS ULTIMT250</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
   </si>
   <si>
     <t>20038425</t>
@@ -226,46 +214,43 @@
     <t>RT,(E-14H)</t>
   </si>
   <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
+  </si>
+  <si>
     <t>20071510</t>
   </si>
   <si>
     <t>NTRVE BNCOL LYCH 100</t>
   </si>
   <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
     <t>20082247</t>
   </si>
   <si>
     <t>NTRVE BNCOL ORG 100</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>10036647</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT CHO1L</t>
-  </si>
-  <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
+    <t>20136649</t>
+  </si>
+  <si>
+    <t>DIAMOND JC CRANBR200</t>
+  </si>
+  <si>
+    <t>20019597</t>
+  </si>
+  <si>
+    <t>MILO ACTIV-GO 180ML</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
   </si>
   <si>
     <t>20070569</t>
@@ -274,28 +259,37 @@
     <t>INDOMLK BANANA 180</t>
   </si>
   <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
-  </si>
-  <si>
-    <t>10014293</t>
-  </si>
-  <si>
-    <t>POP MIE SOTO AYM 75G</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
+  </si>
+  <si>
+    <t>20134673</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT PLN 6X110</t>
+  </si>
+  <si>
+    <t>20121662</t>
+  </si>
+  <si>
+    <t>INDOMLK KD LS CKL115</t>
+  </si>
+  <si>
+    <t>20088789</t>
+  </si>
+  <si>
+    <t>INDOMLK KID F.CRM115</t>
+  </si>
+  <si>
+    <t>20057229</t>
+  </si>
+  <si>
+    <t>VIDORAN SUSU COK 110</t>
   </si>
 </sst>
 </file>
@@ -688,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -756,15 +750,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -773,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -781,10 +775,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -796,15 +790,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -816,15 +810,15 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -833,18 +827,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -853,18 +847,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -873,18 +867,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -893,18 +887,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -913,18 +907,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -933,107 +927,107 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1041,59 +1035,59 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1101,39 +1095,39 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1141,199 +1135,199 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1341,19 +1335,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1361,19 +1355,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1381,19 +1375,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1401,19 +1395,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1421,62 +1415,22 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
   <si>
     <t/>
   </si>
   <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -28,268 +28,175 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20103297</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP200</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20108465</t>
+  </si>
+  <si>
+    <t>DARLIE PG FRS.CLN150</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20035998</t>
+  </si>
+  <si>
+    <t>INDOMRET TRVL PACK50</t>
+  </si>
+  <si>
+    <t>20000765</t>
+  </si>
+  <si>
+    <t>CLEAN&amp;CLEAR FAC 50</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95G</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20084707</t>
+  </si>
+  <si>
+    <t>SUKRO KC OVEN BWG 95</t>
+  </si>
+  <si>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
+  </si>
+  <si>
+    <t>20072316</t>
+  </si>
+  <si>
+    <t>D/K SUKRO KEDELE 95G</t>
+  </si>
+  <si>
+    <t>20035976</t>
+  </si>
+  <si>
+    <t>CAP BTL TEH CLP HJ25</t>
+  </si>
+  <si>
+    <t>20035264</t>
+  </si>
+  <si>
+    <t>IDM KC.ATOM/SHANG140</t>
+  </si>
+  <si>
+    <t>20042632</t>
+  </si>
+  <si>
+    <t>IDM KCG ATOM PDS 140</t>
+  </si>
+  <si>
+    <t>20129288</t>
+  </si>
+  <si>
+    <t>PRMINA CRN CHKN.BR20</t>
+  </si>
+  <si>
+    <t>20094437</t>
+  </si>
+  <si>
+    <t>PROMINA CRUNCHIES 20</t>
+  </si>
+  <si>
+    <t>20129287</t>
+  </si>
+  <si>
+    <t>PRMINA CRN SEAWED 20</t>
+  </si>
+  <si>
+    <t>20138049</t>
+  </si>
+  <si>
+    <t>HY BTS COFF CPNO 250</t>
+  </si>
+  <si>
+    <t>20138025</t>
+  </si>
+  <si>
+    <t>HY BTS COFF TRMS 250</t>
+  </si>
+  <si>
+    <t>20121348</t>
+  </si>
+  <si>
+    <t>LASEGAR TWST J-L 320</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20139699</t>
-  </si>
-  <si>
-    <t>OASIS  MNRL PH9 500</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20134246</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 350ML</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>20132840</t>
-  </si>
-  <si>
-    <t>IDM TEH BLCKCRRNT350</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 250</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 250</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20139550</t>
-  </si>
-  <si>
-    <t>REGEN LMN LIME 300ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20141124</t>
-  </si>
-  <si>
-    <t>REGEN ORANGE 300ML</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138893</t>
-  </si>
-  <si>
-    <t>AMO DRMY STRAW 180ML</t>
-  </si>
-  <si>
-    <t>20138894</t>
-  </si>
-  <si>
-    <t>AMO FIZZY EASY 180ML</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>20089821</t>
-  </si>
-  <si>
-    <t>ORONAMIN C DRINK 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>20138252</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS ULTIMT250</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20038425</t>
-  </si>
-  <si>
-    <t>NTRIVE/B BLCKRNT 100</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
-    <t>20071510</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL LYCH 100</t>
-  </si>
-  <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20136649</t>
-  </si>
-  <si>
-    <t>DIAMOND JC CRANBR200</t>
-  </si>
-  <si>
-    <t>20019597</t>
-  </si>
-  <si>
-    <t>MILO ACTIV-GO 180ML</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
-  </si>
-  <si>
-    <t>20134673</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT PLN 6X110</t>
-  </si>
-  <si>
-    <t>20121662</t>
-  </si>
-  <si>
-    <t>INDOMLK KD LS CKL115</t>
-  </si>
-  <si>
-    <t>20088789</t>
-  </si>
-  <si>
-    <t>INDOMLK KID F.CRM115</t>
-  </si>
-  <si>
-    <t>20057229</t>
-  </si>
-  <si>
-    <t>VIDORAN SUSU COK 110</t>
+    <t>20021257</t>
+  </si>
+  <si>
+    <t>U/BISC BONBON CHO200</t>
+  </si>
+  <si>
+    <t>20063155</t>
+  </si>
+  <si>
+    <t>SOYJOY CKLT ALMND 30</t>
+  </si>
+  <si>
+    <t>20030646</t>
+  </si>
+  <si>
+    <t>SOYJOY STRAWBERRY 30</t>
   </si>
 </sst>
 </file>
@@ -682,15 +589,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -770,15 +676,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -790,15 +696,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -807,18 +713,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -827,18 +733,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -847,18 +753,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -867,50 +773,50 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,513 +830,273 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
   <si>
     <t/>
   </si>
   <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -28,150 +28,162 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20103297</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP200</t>
+    <t>20061938</t>
+  </si>
+  <si>
+    <t>SUPER O2 SPRTVO 600</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20108465</t>
-  </si>
-  <si>
-    <t>DARLIE PG FRS.CLN150</t>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048348</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR500</t>
+  </si>
+  <si>
+    <t>20129966</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 330</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20128821</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO 390ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20130667</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 390</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20129123</t>
+  </si>
+  <si>
+    <t>OATSDE CHOCO 200</t>
+  </si>
+  <si>
+    <t>20129102</t>
+  </si>
+  <si>
+    <t>OATSDE BR.BLEND 200</t>
+  </si>
+  <si>
+    <t>20032519</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK APL140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20136277</t>
+  </si>
+  <si>
+    <t>SNPRD FRT MG.PINE220</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20035998</t>
-  </si>
-  <si>
-    <t>INDOMRET TRVL PACK50</t>
-  </si>
-  <si>
-    <t>20000765</t>
-  </si>
-  <si>
-    <t>CLEAN&amp;CLEAR FAC 50</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20084707</t>
-  </si>
-  <si>
-    <t>SUKRO KC OVEN BWG 95</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
-  </si>
-  <si>
-    <t>20072316</t>
-  </si>
-  <si>
-    <t>D/K SUKRO KEDELE 95G</t>
-  </si>
-  <si>
-    <t>20035976</t>
-  </si>
-  <si>
-    <t>CAP BTL TEH CLP HJ25</t>
-  </si>
-  <si>
-    <t>20035264</t>
-  </si>
-  <si>
-    <t>IDM KC.ATOM/SHANG140</t>
-  </si>
-  <si>
-    <t>20042632</t>
-  </si>
-  <si>
-    <t>IDM KCG ATOM PDS 140</t>
-  </si>
-  <si>
-    <t>20129288</t>
-  </si>
-  <si>
-    <t>PRMINA CRN CHKN.BR20</t>
-  </si>
-  <si>
-    <t>20094437</t>
-  </si>
-  <si>
-    <t>PROMINA CRUNCHIES 20</t>
-  </si>
-  <si>
-    <t>20129287</t>
-  </si>
-  <si>
-    <t>PRMINA CRN SEAWED 20</t>
-  </si>
-  <si>
-    <t>20138049</t>
-  </si>
-  <si>
-    <t>HY BTS COFF CPNO 250</t>
-  </si>
-  <si>
-    <t>20138025</t>
-  </si>
-  <si>
-    <t>HY BTS COFF TRMS 250</t>
-  </si>
-  <si>
     <t>20121348</t>
   </si>
   <si>
@@ -181,22 +193,70 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20021257</t>
-  </si>
-  <si>
-    <t>U/BISC BONBON CHO200</t>
-  </si>
-  <si>
-    <t>20063155</t>
-  </si>
-  <si>
-    <t>SOYJOY CKLT ALMND 30</t>
-  </si>
-  <si>
-    <t>20030646</t>
-  </si>
-  <si>
-    <t>SOYJOY STRAWBERRY 30</t>
+    <t>10000107</t>
+  </si>
+  <si>
+    <t>GREEN SAND ORGNL 330</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>20056989</t>
+  </si>
+  <si>
+    <t>RED BULL GOLD 250ML</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>10004884</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CHO 950</t>
+  </si>
+  <si>
+    <t>10005909</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT PLN 950</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>20112746</t>
+  </si>
+  <si>
+    <t>INDOMLK KIDS CKLT 6S</t>
+  </si>
+  <si>
+    <t>20112794</t>
+  </si>
+  <si>
+    <t>INDOMLK KIDS STRW 6S</t>
+  </si>
+  <si>
+    <t>20138376</t>
+  </si>
+  <si>
+    <t>BEBELAC 1 UHT 105ML</t>
   </si>
 </sst>
 </file>
@@ -589,14 +649,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -656,15 +716,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -673,18 +733,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -696,15 +756,15 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -713,18 +773,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -733,18 +793,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -753,18 +813,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -773,330 +833,510 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>55</v>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,21 +11,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="89">
   <si>
     <t/>
   </si>
   <si>
+    <t>20133979</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 1LT</t>
+  </si>
+  <si>
+    <t>EG2B</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20036198</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO PET1L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>20005529</t>
   </si>
   <si>
     <t>NESTLE PURE LIFE 600</t>
   </si>
   <si>
-    <t>EG2B</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -37,130 +58,160 @@
     <t>CRYSTALIN BTL 600mL</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20061938</t>
-  </si>
-  <si>
-    <t>SUPER O2 SPRTVO 600</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048348</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR500</t>
-  </si>
-  <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MINUMAN LIME 330</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
+  </si>
+  <si>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>20056219</t>
+  </si>
+  <si>
+    <t>ETERNALPLUS BTL 500</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
+  </si>
+  <si>
+    <t>20127835</t>
+  </si>
+  <si>
+    <t>ALANG SARI JN 300ML</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20128821</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO 390ML</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20062818</t>
+  </si>
+  <si>
+    <t>FRUITAMIN LYCHE 350</t>
+  </si>
+  <si>
+    <t>20140327</t>
+  </si>
+  <si>
+    <t>COCO BIT KY.GRP 350</t>
+  </si>
+  <si>
+    <t>20037136</t>
+  </si>
+  <si>
+    <t>PORORO SUSU 235ML</t>
+  </si>
+  <si>
+    <t>20037137</t>
+  </si>
+  <si>
+    <t>PORORO STROBRI 235ML</t>
+  </si>
+  <si>
+    <t>20085010</t>
+  </si>
+  <si>
+    <t>PORORO MANGO 235</t>
+  </si>
+  <si>
+    <t>20038425</t>
+  </si>
+  <si>
+    <t>NTRIVE/B BLCKRNT 100</t>
+  </si>
+  <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20130667</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 390</t>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20141980</t>
-  </si>
-  <si>
-    <t>DUM2 RYL MILK TEA330</t>
-  </si>
-  <si>
-    <t>20141981</t>
-  </si>
-  <si>
-    <t>DUM2 CHO MILK TEA330</t>
-  </si>
-  <si>
-    <t>20129123</t>
-  </si>
-  <si>
-    <t>OATSDE CHOCO 200</t>
-  </si>
-  <si>
-    <t>20129102</t>
-  </si>
-  <si>
-    <t>OATSDE BR.BLEND 200</t>
-  </si>
-  <si>
-    <t>20032519</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK APL140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20045415</t>
+  </si>
+  <si>
+    <t>KOPIKO 78C 240ML</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20113450</t>
+  </si>
+  <si>
+    <t>ICHITAN MLK BRWN 300</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20085054</t>
+  </si>
+  <si>
+    <t>ICHTN THAI M.TEA 300</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
   </si>
   <si>
     <t>20069199</t>
@@ -169,94 +220,64 @@
     <t>KAKI3 LMN.LM KLG 320</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20136277</t>
-  </si>
-  <si>
-    <t>SNPRD FRT MG.PINE220</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20121348</t>
-  </si>
-  <si>
-    <t>LASEGAR TWST J-L 320</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000107</t>
-  </si>
-  <si>
-    <t>GREEN SAND ORGNL 330</t>
-  </si>
-  <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>20056989</t>
-  </si>
-  <si>
-    <t>RED BULL GOLD 250ML</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>10004884</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CHO 950</t>
-  </si>
-  <si>
-    <t>10005909</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT PLN 950</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
-  </si>
-  <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>20112746</t>
-  </si>
-  <si>
-    <t>INDOMLK KIDS CKLT 6S</t>
-  </si>
-  <si>
-    <t>20112794</t>
-  </si>
-  <si>
-    <t>INDOMLK KIDS STRW 6S</t>
-  </si>
-  <si>
-    <t>20138376</t>
-  </si>
-  <si>
-    <t>BEBELAC 1 UHT 105ML</t>
+    <t>20037147</t>
+  </si>
+  <si>
+    <t>KAKI TIGA STRO 320ML</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20117682</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA RD.VEL240</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>20127735</t>
+  </si>
+  <si>
+    <t>INDMLK DLGNA COFF180</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>10036647</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT CHO1L</t>
+  </si>
+  <si>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
+  </si>
+  <si>
+    <t>20091183</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT STR 6X110</t>
+  </si>
+  <si>
+    <t>20113180</t>
+  </si>
+  <si>
+    <t>MILO COKLAT 4X110ML</t>
   </si>
 </sst>
 </file>
@@ -649,14 +670,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -736,55 +758,55 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -793,18 +815,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -813,18 +835,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -833,18 +855,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -853,10 +875,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -873,18 +895,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -893,10 +915,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -916,7 +938,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -956,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -973,10 +995,10 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -993,10 +1015,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1013,7 +1035,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1033,7 +1055,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1041,10 +1063,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1053,18 +1075,18 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1073,270 +1095,310 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
   <si>
     <t/>
   </si>
   <si>
-    <t>20133979</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 1LT</t>
+    <t>20135615</t>
+  </si>
+  <si>
+    <t>CAT CHOIZE+T&amp;S 1.2KG</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -28,256 +28,157 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20036198</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO PET1L</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20088717</t>
+  </si>
+  <si>
+    <t>ME-O CAT FD TUNA 200</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20108465</t>
+  </si>
+  <si>
+    <t>DARLIE PG FRS.CLN150</t>
+  </si>
+  <si>
+    <t>20137311</t>
+  </si>
+  <si>
+    <t>MY BBY KD KY PTH 150</t>
+  </si>
+  <si>
+    <t>20093587</t>
+  </si>
+  <si>
+    <t>SENKA PRFCT WHIP 50</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20105569</t>
+  </si>
+  <si>
+    <t>EMCO DORAEMON MN FGR</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20134354</t>
+  </si>
+  <si>
+    <t>IDM SARI BH NANAS220</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20139699</t>
-  </si>
-  <si>
-    <t>OASIS  MNRL PH9 500</t>
-  </si>
-  <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20056219</t>
-  </si>
-  <si>
-    <t>ETERNALPLUS BTL 500</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20127835</t>
-  </si>
-  <si>
-    <t>ALANG SARI JN 300ML</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20062818</t>
-  </si>
-  <si>
-    <t>FRUITAMIN LYCHE 350</t>
-  </si>
-  <si>
-    <t>20140327</t>
-  </si>
-  <si>
-    <t>COCO BIT KY.GRP 350</t>
-  </si>
-  <si>
-    <t>20037136</t>
-  </si>
-  <si>
-    <t>PORORO SUSU 235ML</t>
-  </si>
-  <si>
-    <t>20037137</t>
-  </si>
-  <si>
-    <t>PORORO STROBRI 235ML</t>
-  </si>
-  <si>
-    <t>20085010</t>
-  </si>
-  <si>
-    <t>PORORO MANGO 235</t>
-  </si>
-  <si>
-    <t>20038425</t>
-  </si>
-  <si>
-    <t>NTRIVE/B BLCKRNT 100</t>
-  </si>
-  <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20045415</t>
-  </si>
-  <si>
-    <t>KOPIKO 78C 240ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20113450</t>
-  </si>
-  <si>
-    <t>ICHITAN MLK BRWN 300</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20085054</t>
-  </si>
-  <si>
-    <t>ICHTN THAI M.TEA 300</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20037147</t>
-  </si>
-  <si>
-    <t>KAKI TIGA STRO 320ML</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
-  </si>
-  <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>20127735</t>
-  </si>
-  <si>
-    <t>INDMLK DLGNA COFF180</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>10036647</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT CHO1L</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
-  </si>
-  <si>
-    <t>20091183</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT STR 6X110</t>
-  </si>
-  <si>
-    <t>20113180</t>
-  </si>
-  <si>
-    <t>MILO COKLAT 4X110ML</t>
+    <t>20134353</t>
+  </si>
+  <si>
+    <t>IDM S/B NNS&amp;MRKSA220</t>
+  </si>
+  <si>
+    <t>20026676</t>
+  </si>
+  <si>
+    <t>INDOMARET GARAM 500G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20139346</t>
+  </si>
+  <si>
+    <t>LARISST GRM KASAR500</t>
+  </si>
+  <si>
+    <t>20140264</t>
+  </si>
+  <si>
+    <t>CHIKI NUTTY CRML 50G</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20021257</t>
+  </si>
+  <si>
+    <t>U/BISC BONBON CHO200</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
+    <t>20092546</t>
+  </si>
+  <si>
+    <t>SLVR QUEEN MATCHA 22</t>
   </si>
 </sst>
 </file>
@@ -670,15 +571,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -738,15 +638,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -755,30 +655,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -792,21 +692,21 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -815,50 +715,50 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -875,18 +775,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -895,147 +795,147 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1043,362 +943,62 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="102">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135615</t>
-  </si>
-  <si>
-    <t>CAT CHOIZE+T&amp;S 1.2KG</t>
+    <t>10004337</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR/MN1500</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -28,157 +28,295 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20046841</t>
+  </si>
+  <si>
+    <t>BIG COLA BTL 3.1L</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20046842</t>
+  </si>
+  <si>
+    <t>BIG STRAW BTL 3.1L</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20135311</t>
+  </si>
+  <si>
+    <t>HYDROPL ISTNC JRK350</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20088717</t>
-  </si>
-  <si>
-    <t>ME-O CAT FD TUNA 200</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20141980</t>
+  </si>
+  <si>
+    <t>DUM2 RYL MILK TEA330</t>
+  </si>
+  <si>
+    <t>20141981</t>
+  </si>
+  <si>
+    <t>DUM2 CHO MILK TEA330</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>10028190</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS KLG 250</t>
+  </si>
+  <si>
+    <t>20052734</t>
+  </si>
+  <si>
+    <t>LOTTE MILKIS MLN 250</t>
+  </si>
+  <si>
+    <t>20046319</t>
+  </si>
+  <si>
+    <t>PANDA GRASS JELY310</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20140802</t>
-  </si>
-  <si>
-    <t>IDM TISU DAPUR 1+1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20108465</t>
-  </si>
-  <si>
-    <t>DARLIE PG FRS.CLN150</t>
-  </si>
-  <si>
-    <t>20137311</t>
-  </si>
-  <si>
-    <t>MY BBY KD KY PTH 150</t>
-  </si>
-  <si>
-    <t>20093587</t>
-  </si>
-  <si>
-    <t>SENKA PRFCT WHIP 50</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20105569</t>
-  </si>
-  <si>
-    <t>EMCO DORAEMON MN FGR</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20134354</t>
-  </si>
-  <si>
-    <t>IDM SARI BH NANAS220</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20134353</t>
-  </si>
-  <si>
-    <t>IDM S/B NNS&amp;MRKSA220</t>
-  </si>
-  <si>
-    <t>20026676</t>
-  </si>
-  <si>
-    <t>INDOMARET GARAM 500G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20139346</t>
-  </si>
-  <si>
-    <t>LARISST GRM KASAR500</t>
-  </si>
-  <si>
-    <t>20140264</t>
-  </si>
-  <si>
-    <t>CHIKI NUTTY CRML 50G</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20021257</t>
-  </si>
-  <si>
-    <t>U/BISC BONBON CHO200</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>20092546</t>
-  </si>
-  <si>
-    <t>SLVR QUEEN MATCHA 22</t>
+    <t>20120929</t>
+  </si>
+  <si>
+    <t>PANDA GR.JLY+BSL 310</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20136277</t>
+  </si>
+  <si>
+    <t>SNPRD FRT MG.PINE220</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 200</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
+  </si>
+  <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20124713</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 220</t>
+  </si>
+  <si>
+    <t>20132761</t>
+  </si>
+  <si>
+    <t>CAFINO RTD CPCINO200</t>
+  </si>
+  <si>
+    <t>20132760</t>
+  </si>
+  <si>
+    <t>CAFINO RTD ESPRSO200</t>
+  </si>
+  <si>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
+  </si>
+  <si>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
+  </si>
+  <si>
+    <t>20025753</t>
+  </si>
+  <si>
+    <t>F/F L/FAT COK TPK225</t>
+  </si>
+  <si>
+    <t>20070253</t>
+  </si>
+  <si>
+    <t>FF COCONUT TPK 225ML</t>
+  </si>
+  <si>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
+  </si>
+  <si>
+    <t>20091183</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT STR 6X110</t>
+  </si>
+  <si>
+    <t>20121662</t>
+  </si>
+  <si>
+    <t>INDOMLK KD LS CKL115</t>
+  </si>
+  <si>
+    <t>10004778</t>
+  </si>
+  <si>
+    <t>INDOMILK KID VNL 115</t>
   </si>
 </sst>
 </file>
@@ -571,14 +709,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -658,27 +797,27 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -692,21 +831,21 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -715,18 +854,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -735,10 +874,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -755,10 +894,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -775,18 +914,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -795,58 +934,58 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -855,150 +994,590 @@
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>37</v>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -205,13 +205,13 @@
     <t>20102789</t>
   </si>
   <si>
-    <t>ABC CHOCMLT COFF 200</t>
+    <t>ABC CHOCMLT COFF 180</t>
   </si>
   <si>
     <t>20102790</t>
   </si>
   <si>
-    <t>ABC MILK COFFEE 200</t>
+    <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
     <t>20078206</t>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="98">
   <si>
     <t/>
   </si>
   <si>
-    <t>20074710</t>
-  </si>
-  <si>
-    <t>IDM KESET HANDUK</t>
+    <t>20104405</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 32-M</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -31,13 +31,79 @@
     <t>PT</t>
   </si>
   <si>
+    <t>20136043</t>
+  </si>
+  <si>
+    <t>FITTI PNTS 40S/SMALL</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20104406</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 28-L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20104407</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 26-XL</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20132816</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 24'S XXL</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20136272</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/M</t>
+  </si>
+  <si>
+    <t>20136273</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/L</t>
+  </si>
+  <si>
+    <t>20136274</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMX HTM/XL</t>
+  </si>
+  <si>
     <t>20134078</t>
   </si>
   <si>
     <t>IDM BOXER PRIA MAX M</t>
   </si>
   <si>
-    <t>2</t>
+    <t>20134079</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX L</t>
+  </si>
+  <si>
+    <t>20134080</t>
+  </si>
+  <si>
+    <t>IDM BXER PRIA MAX XL</t>
   </si>
   <si>
     <t>20134081</t>
@@ -46,7 +112,10 @@
     <t>IDM CLMAX BRIEF M 2S</t>
   </si>
   <si>
-    <t>3</t>
+    <t>20134082</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF L 2S</t>
   </si>
   <si>
     <t>20134083</t>
@@ -55,16 +124,10 @@
     <t>IDM CLMAX BRIEF XL2S</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20139598</t>
-  </si>
-  <si>
-    <t>SNSLK SHP AD&amp;SLK 320</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
+    <t>20094320</t>
+  </si>
+  <si>
+    <t>CLEAR SHP LEMON 160</t>
   </si>
   <si>
     <t>20138649</t>
@@ -76,81 +139,162 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10003391</t>
-  </si>
-  <si>
-    <t>MS.RATU SHMP BYM 175</t>
-  </si>
-  <si>
-    <t>20136299</t>
-  </si>
-  <si>
-    <t>SUNSLK HR PRFM 100ML</t>
+    <t>20138036</t>
+  </si>
+  <si>
+    <t>SUNSLK VIIT S.GL 100</t>
+  </si>
+  <si>
+    <t>20048965</t>
+  </si>
+  <si>
+    <t>DOVE DEO ULTM.RP 40</t>
+  </si>
+  <si>
+    <t>20139354</t>
+  </si>
+  <si>
+    <t>RXONA MEN FR.STRK 40</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138036</t>
-  </si>
-  <si>
-    <t>SUNSLK VIIT S.GL 100</t>
-  </si>
-  <si>
-    <t>20111611</t>
-  </si>
-  <si>
-    <t>GARNIER HC NAT 6.64</t>
+    <t>20132165</t>
+  </si>
+  <si>
+    <t>CULTUSIA SHP BLACK25</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20017141</t>
+  </si>
+  <si>
+    <t>PPSODENT PG C.FRS160</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20119092</t>
-  </si>
-  <si>
-    <t>PSODENT SG SIWAK 2'S</t>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20100788</t>
+  </si>
+  <si>
+    <t>PSODENT PG SIWAK 150</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20129578</t>
+  </si>
+  <si>
+    <t>GATSBY BALM PMADE 70</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20127064</t>
+  </si>
+  <si>
+    <t>S/R STYLING PMDE 75</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135463</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CHO.HZL180</t>
+  </si>
+  <si>
+    <t>20135462</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CKS&amp;CRM180</t>
+  </si>
+  <si>
+    <t>20138477</t>
+  </si>
+  <si>
+    <t>DANCOW CHO.CR 346.5G</t>
+  </si>
+  <si>
     <t>20133914</t>
   </si>
   <si>
     <t>IDM CHKPEAS JG.BKR60</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20135618</t>
   </si>
   <si>
     <t>LRSST FRNCH ORIGNL65</t>
   </si>
   <si>
+    <t>20140451</t>
+  </si>
+  <si>
+    <t>IDM STICK CRML 18S</t>
+  </si>
+  <si>
     <t>20140455</t>
   </si>
   <si>
     <t>IDM STICK CKLT 18S</t>
   </si>
   <si>
-    <t>20140451</t>
-  </si>
-  <si>
-    <t>IDM STICK CRML 18S</t>
-  </si>
-  <si>
     <t>20043409</t>
   </si>
   <si>
     <t>IDM BIHUN BERAS 220G</t>
   </si>
   <si>
+    <t>20140633</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG SPC 5S</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20140657</t>
+  </si>
+  <si>
+    <t>INDOMIE AYAM BWG 5S</t>
+  </si>
+  <si>
+    <t>20133372</t>
+  </si>
+  <si>
+    <t>INDOMIE RWN MERCON75</t>
+  </si>
+  <si>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
+  </si>
+  <si>
     <t>20032996</t>
   </si>
   <si>
@@ -161,27 +305,6 @@
   </si>
   <si>
     <t>PALDO BIBMEN II 130G</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
   </si>
 </sst>
 </file>
@@ -574,13 +697,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -638,10 +762,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -695,33 +819,33 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -735,13 +859,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -755,81 +879,81 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -838,18 +962,18 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -858,18 +982,18 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -878,38 +1002,38 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -918,18 +1042,18 @@
         <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -938,18 +1062,18 @@
         <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -958,70 +1082,430 @@
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>52</v>
+      <c r="E23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t/>
   </si>
@@ -145,127 +145,109 @@
     <t>SUNSLK VIIT S.GL 100</t>
   </si>
   <si>
-    <t>20048965</t>
-  </si>
-  <si>
-    <t>DOVE DEO ULTM.RP 40</t>
-  </si>
-  <si>
-    <t>20139354</t>
-  </si>
-  <si>
-    <t>RXONA MEN FR.STRK 40</t>
+    <t>20132165</t>
+  </si>
+  <si>
+    <t>CULTUSIA SHP BLACK25</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20017141</t>
+  </si>
+  <si>
+    <t>PPSODENT PG C.FRS160</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20100788</t>
+  </si>
+  <si>
+    <t>PSODENT PG SIWAK 150</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20129578</t>
+  </si>
+  <si>
+    <t>GATSBY BALM PMADE 70</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20127064</t>
+  </si>
+  <si>
+    <t>S/R STYLING PMDE 75</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135463</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CHO.HZL180</t>
+  </si>
+  <si>
+    <t>20135462</t>
+  </si>
+  <si>
+    <t>DNCW MLKY CKS&amp;CRM180</t>
+  </si>
+  <si>
+    <t>20138477</t>
+  </si>
+  <si>
+    <t>DANCOW CHO.CR 346.5G</t>
+  </si>
+  <si>
+    <t>20135618</t>
+  </si>
+  <si>
+    <t>LRSST FRNCH ORIGNL65</t>
+  </si>
+  <si>
+    <t>20140451</t>
+  </si>
+  <si>
+    <t>IDM STICK CRML 18S</t>
+  </si>
+  <si>
+    <t>20140455</t>
+  </si>
+  <si>
+    <t>IDM STICK CKLT 18S</t>
+  </si>
+  <si>
+    <t>20043409</t>
+  </si>
+  <si>
+    <t>IDM BIHUN BERAS 220G</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>20132165</t>
-  </si>
-  <si>
-    <t>CULTUSIA SHP BLACK25</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20017141</t>
-  </si>
-  <si>
-    <t>PPSODENT PG C.FRS160</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20100788</t>
-  </si>
-  <si>
-    <t>PSODENT PG SIWAK 150</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20129578</t>
-  </si>
-  <si>
-    <t>GATSBY BALM PMADE 70</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20127064</t>
-  </si>
-  <si>
-    <t>S/R STYLING PMDE 75</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135463</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CHO.HZL180</t>
-  </si>
-  <si>
-    <t>20135462</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CKS&amp;CRM180</t>
-  </si>
-  <si>
-    <t>20138477</t>
-  </si>
-  <si>
-    <t>DANCOW CHO.CR 346.5G</t>
-  </si>
-  <si>
-    <t>20133914</t>
-  </si>
-  <si>
-    <t>IDM CHKPEAS JG.BKR60</t>
-  </si>
-  <si>
-    <t>20135618</t>
-  </si>
-  <si>
-    <t>LRSST FRNCH ORIGNL65</t>
-  </si>
-  <si>
-    <t>20140451</t>
-  </si>
-  <si>
-    <t>IDM STICK CRML 18S</t>
-  </si>
-  <si>
-    <t>20140455</t>
-  </si>
-  <si>
-    <t>IDM STICK CKLT 18S</t>
-  </si>
-  <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
   </si>
   <si>
     <t>20140633</t>
@@ -697,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1082,18 +1064,18 @@
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1102,18 +1084,18 @@
         <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1122,18 +1104,18 @@
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1142,18 +1124,18 @@
         <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1162,50 +1144,50 @@
         <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1222,18 +1204,18 @@
         <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1242,18 +1224,18 @@
         <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1262,18 +1244,18 @@
         <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1282,18 +1264,18 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1302,30 +1284,30 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1339,73 +1321,73 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1419,13 +1401,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1439,72 +1421,12 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="1" t="s">
         <v>41</v>
       </c>
     </row>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t/>
   </si>
@@ -679,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -687,10 +687,11 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -709,8 +710,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -726,11 +733,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -746,11 +753,11 @@
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -766,11 +773,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -786,11 +793,11 @@
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -806,11 +813,11 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -826,11 +833,11 @@
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -846,11 +853,11 @@
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -866,11 +873,11 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -886,11 +893,11 @@
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -906,11 +913,11 @@
       <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -926,11 +933,11 @@
       <c r="E12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -946,11 +953,11 @@
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -966,11 +973,11 @@
       <c r="E14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -986,11 +993,11 @@
       <c r="E15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -1006,11 +1013,11 @@
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -1026,11 +1033,11 @@
       <c r="E17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -1046,11 +1053,11 @@
       <c r="E18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -1066,11 +1073,11 @@
       <c r="E19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>47</v>
       </c>
@@ -1086,11 +1093,11 @@
       <c r="E20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -1106,11 +1113,11 @@
       <c r="E21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -1126,11 +1133,11 @@
       <c r="E22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
@@ -1146,11 +1153,11 @@
       <c r="E23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
@@ -1166,11 +1173,11 @@
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
@@ -1186,11 +1193,11 @@
       <c r="E25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>66</v>
       </c>
@@ -1206,11 +1213,11 @@
       <c r="E26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>68</v>
       </c>
@@ -1226,11 +1233,11 @@
       <c r="E27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>70</v>
       </c>
@@ -1246,11 +1253,11 @@
       <c r="E28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>72</v>
       </c>
@@ -1266,11 +1273,11 @@
       <c r="E29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -1286,11 +1293,11 @@
       <c r="E30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>76</v>
       </c>
@@ -1306,11 +1313,11 @@
       <c r="E31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>79</v>
       </c>
@@ -1326,11 +1333,11 @@
       <c r="E32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -1346,11 +1353,11 @@
       <c r="E33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
@@ -1366,11 +1373,11 @@
       <c r="E34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>86</v>
       </c>
@@ -1386,11 +1393,11 @@
       <c r="E35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>88</v>
       </c>
@@ -1406,11 +1413,11 @@
       <c r="E36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>90</v>
       </c>
@@ -1426,7 +1433,7 @@
       <c r="E37" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>41</v>
       </c>
     </row>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
   <si>
     <t/>
   </si>
@@ -31,6 +31,36 @@
     <t>PT</t>
   </si>
   <si>
+    <t>20104406</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 28-L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20104407</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 26-XL</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20132816</t>
+  </si>
+  <si>
+    <t>FITTI PANTS 24'S XXL</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
     <t>20136043</t>
   </si>
   <si>
@@ -40,34 +70,40 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20104406</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 28-L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20104407</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 26-XL</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20132816</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 24'S XXL</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
+    <t>20134078</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX M</t>
+  </si>
+  <si>
+    <t>20134079</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX L</t>
+  </si>
+  <si>
+    <t>20134080</t>
+  </si>
+  <si>
+    <t>IDM BXER PRIA MAX XL</t>
+  </si>
+  <si>
+    <t>20134081</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF M 2S</t>
+  </si>
+  <si>
+    <t>20134082</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF L 2S</t>
+  </si>
+  <si>
+    <t>20134083</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF XL2S</t>
   </si>
   <si>
     <t>20136272</t>
@@ -88,40 +124,88 @@
     <t>IDM KAOS CLMX HTM/XL</t>
   </si>
   <si>
-    <t>20134078</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX M</t>
-  </si>
-  <si>
-    <t>20134079</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX L</t>
-  </si>
-  <si>
-    <t>20134080</t>
-  </si>
-  <si>
-    <t>IDM BXER PRIA MAX XL</t>
-  </si>
-  <si>
-    <t>20134081</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF M 2S</t>
-  </si>
-  <si>
-    <t>20134082</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF L 2S</t>
-  </si>
-  <si>
-    <t>20134083</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF XL2S</t>
+    <t>20017141</t>
+  </si>
+  <si>
+    <t>PPSODENT PG C.FRS160</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20100788</t>
+  </si>
+  <si>
+    <t>PSODENT PG SIWAK 150</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>20132664</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT SEGAR 600</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
+  </si>
+  <si>
+    <t>20088537</t>
+  </si>
+  <si>
+    <t>GRNR VIT.C SPF36-20</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20090447</t>
+  </si>
+  <si>
+    <t>GRNR SRM CR SPF30-20</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20138036</t>
+  </si>
+  <si>
+    <t>SUNSLK VIIT S.GL 100</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>20094320</t>
@@ -130,19 +214,25 @@
     <t>CLEAR SHP LEMON 160</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>20138649</t>
   </si>
   <si>
     <t>EMRN SHP BT21 AK 340</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138036</t>
-  </si>
-  <si>
-    <t>SUNSLK VIIT S.GL 100</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20127064</t>
+  </si>
+  <si>
+    <t>S/R STYLING PMDE 75</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>20132165</t>
@@ -151,82 +241,25 @@
     <t>CULTUSIA SHP BLACK25</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20017141</t>
-  </si>
-  <si>
-    <t>PPSODENT PG C.FRS160</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20100788</t>
-  </si>
-  <si>
-    <t>PSODENT PG SIWAK 150</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20129578</t>
-  </si>
-  <si>
-    <t>GATSBY BALM PMADE 70</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20127064</t>
-  </si>
-  <si>
-    <t>S/R STYLING PMDE 75</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20138477</t>
+  </si>
+  <si>
+    <t>DANCOW CHO.CR 346.5G</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20135463</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CHO.HZL180</t>
-  </si>
-  <si>
-    <t>20135462</t>
-  </si>
-  <si>
-    <t>DNCW MLKY CKS&amp;CRM180</t>
-  </si>
-  <si>
-    <t>20138477</t>
-  </si>
-  <si>
-    <t>DANCOW CHO.CR 346.5G</t>
-  </si>
-  <si>
-    <t>20135618</t>
-  </si>
-  <si>
-    <t>LRSST FRNCH ORIGNL65</t>
+    <t>20094328</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPREK 65</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
   </si>
   <si>
     <t>20140451</t>
@@ -239,54 +272,6 @@
   </si>
   <si>
     <t>IDM STICK CKLT 18S</t>
-  </si>
-  <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20140633</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG SPC 5S</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20140657</t>
-  </si>
-  <si>
-    <t>INDOMIE AYAM BWG 5S</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>20032996</t>
-  </si>
-  <si>
-    <t>PALDO HOT&amp;SPICY 120</t>
-  </si>
-  <si>
-    <t>20138114</t>
-  </si>
-  <si>
-    <t>PALDO BIBMEN II 130G</t>
   </si>
 </sst>
 </file>
@@ -679,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -687,11 +672,10 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -710,14 +694,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -733,11 +711,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -751,13 +729,13 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -773,11 +751,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -793,16 +771,16 @@
       <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -811,13 +789,13 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -828,16 +806,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -848,16 +826,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -868,16 +846,16 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -888,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -908,16 +886,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -928,16 +906,16 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -948,16 +926,16 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -968,16 +946,16 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -988,16 +966,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -1008,36 +986,36 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -1048,16 +1026,16 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -1068,216 +1046,216 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="F24" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="F28" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -1288,153 +1266,93 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="F31" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
   <si>
     <t/>
   </si>
@@ -199,42 +199,6 @@
     <t>RT,(E-3.5B)</t>
   </si>
   <si>
-    <t>20138036</t>
-  </si>
-  <si>
-    <t>SUNSLK VIIT S.GL 100</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20094320</t>
-  </si>
-  <si>
-    <t>CLEAR SHP LEMON 160</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20138649</t>
-  </si>
-  <si>
-    <t>EMRN SHP BT21 AK 340</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20127064</t>
-  </si>
-  <si>
-    <t>S/R STYLING PMDE 75</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20132165</t>
   </si>
   <si>
@@ -260,18 +224,6 @@
   </si>
   <si>
     <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20140451</t>
-  </si>
-  <si>
-    <t>IDM STICK CRML 18S</t>
-  </si>
-  <si>
-    <t>20140455</t>
-  </si>
-  <si>
-    <t>IDM STICK CKLT 18S</t>
   </si>
 </sst>
 </file>
@@ -664,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1192,7 +1144,7 @@
         <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1206,13 +1158,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1226,133 +1178,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,24 +11,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="110">
   <si>
     <t/>
   </si>
   <si>
+    <t>20132664</t>
+  </si>
+  <si>
+    <t>VIXAL KUAT SEGAR 600</t>
+  </si>
+  <si>
+    <t>EG2B</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>20104405</t>
   </si>
   <si>
     <t>FITTI PANTS 32-M</t>
   </si>
   <si>
-    <t>EG2B</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>4</t>
   </si>
   <si>
     <t>20104406</t>
@@ -37,16 +64,13 @@
     <t>FITTI PANTS 28-L</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>20104407</t>
   </si>
   <si>
     <t>FITTI PANTS 26-XL</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>20132816</t>
@@ -55,9 +79,6 @@
     <t>FITTI PANTS 24'S XXL</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
@@ -124,6 +145,84 @@
     <t>IDM KAOS CLMX HTM/XL</t>
   </si>
   <si>
+    <t>20139172</t>
+  </si>
+  <si>
+    <t>G2G VITA C MOIST 30G</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20088537</t>
+  </si>
+  <si>
+    <t>GRNR VIT.C SPF36-20</t>
+  </si>
+  <si>
+    <t>20090447</t>
+  </si>
+  <si>
+    <t>GRNR SRM CR SPF30-20</t>
+  </si>
+  <si>
+    <t>20139173</t>
+  </si>
+  <si>
+    <t>G2G FW P.VITA C 80G</t>
+  </si>
+  <si>
+    <t>20141637</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW FIFA 85G</t>
+  </si>
+  <si>
+    <t>20141638</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW FIFA 500</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20141446</t>
+  </si>
+  <si>
+    <t>LFBUOY BW FIFA 360G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20044015</t>
+  </si>
+  <si>
+    <t>DOVE NOUR. B/WSH 400</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20026897</t>
+  </si>
+  <si>
+    <t>TESSA FAC.TISSUE 260</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20141838</t>
+  </si>
+  <si>
+    <t>PEPSODENT SG FIFA 1S</t>
+  </si>
+  <si>
     <t>20017141</t>
   </si>
   <si>
@@ -139,24 +238,6 @@
     <t>PSODENT PG SIWAK 150</t>
   </si>
   <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
-    <t>20132664</t>
-  </si>
-  <si>
-    <t>VIXAL KUAT SEGAR 600</t>
-  </si>
-  <si>
     <t>20141837</t>
   </si>
   <si>
@@ -169,52 +250,76 @@
     <t>CLOSEUP PG FIFA 95G</t>
   </si>
   <si>
-    <t>20088537</t>
-  </si>
-  <si>
-    <t>GRNR VIT.C SPF36-20</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20090447</t>
-  </si>
-  <si>
-    <t>GRNR SRM CR SPF30-20</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20132165</t>
-  </si>
-  <si>
-    <t>CULTUSIA SHP BLACK25</t>
+    <t>20127770</t>
+  </si>
+  <si>
+    <t>KODOMO P/G STRAWB 80</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20134841</t>
+  </si>
+  <si>
+    <t>CUSSONS TELON PLS 60</t>
+  </si>
+  <si>
+    <t>20137313</t>
+  </si>
+  <si>
+    <t>HANSPLST ANTSP 40ML</t>
+  </si>
+  <si>
+    <t>20108002</t>
+  </si>
+  <si>
+    <t>DOREMI H&amp;B WASH 200</t>
+  </si>
+  <si>
+    <t>20138274</t>
+  </si>
+  <si>
+    <t>ZWTSAL KIDS GREEN280</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20138275</t>
+  </si>
+  <si>
+    <t>ZWITSAL KIDS PINK280</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20138477</t>
-  </si>
-  <si>
-    <t>DANCOW CHO.CR 346.5G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>20108003</t>
+  </si>
+  <si>
+    <t>DOREMI COLG HJB 100</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20019179</t>
+  </si>
+  <si>
+    <t>B/BRAND GOLD MALT140</t>
+  </si>
+  <si>
+    <t>20067201</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGO TPK 1L</t>
+  </si>
+  <si>
+    <t>20115157</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE 1L</t>
   </si>
   <si>
     <t>20094328</t>
@@ -224,6 +329,18 @@
   </si>
   <si>
     <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
+  </si>
+  <si>
+    <t>20037159</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 18X20</t>
   </si>
 </sst>
 </file>
@@ -616,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -624,7 +741,7 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -724,15 +841,15 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -744,24 +861,24 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -769,22 +886,22 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -798,21 +915,21 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -821,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -829,10 +946,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -841,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -849,10 +966,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -861,7 +978,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -869,10 +986,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -881,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -889,10 +1006,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -901,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -909,10 +1026,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -921,7 +1038,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -929,22 +1046,22 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -958,13 +1075,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -978,10 +1095,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1001,18 +1118,18 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1021,70 +1138,70 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1098,13 +1215,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1118,50 +1235,50 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>67</v>
@@ -1178,13 +1295,353 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F33" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>70</v>
+      <c r="F41" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
   <si>
     <t/>
   </si>
@@ -40,292 +40,208 @@
     <t>2</t>
   </si>
   <si>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 610</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
     <t>20128374</t>
   </si>
   <si>
     <t>LFEBUOY REF LIME 650</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20104405</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 32-M</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>20104406</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 28-L</t>
-  </si>
-  <si>
-    <t>20104407</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 26-XL</t>
+    <t>20134081</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF M 2S</t>
+  </si>
+  <si>
+    <t>20134082</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF L 2S</t>
+  </si>
+  <si>
+    <t>20134083</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF XL2S</t>
+  </si>
+  <si>
+    <t>20134078</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX M</t>
+  </si>
+  <si>
+    <t>20134079</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX L</t>
+  </si>
+  <si>
+    <t>20134080</t>
+  </si>
+  <si>
+    <t>IDM BXER PRIA MAX XL</t>
+  </si>
+  <si>
+    <t>20136272</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/M</t>
+  </si>
+  <si>
+    <t>20136273</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/L</t>
+  </si>
+  <si>
+    <t>20136274</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMX HTM/XL</t>
+  </si>
+  <si>
+    <t>20141638</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW FIFA 500</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20141446</t>
+  </si>
+  <si>
+    <t>LFBUOY BW FIFA 360G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141637</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW FIFA 85G</t>
+  </si>
+  <si>
+    <t>20130843</t>
+  </si>
+  <si>
+    <t>CHARM DN SRH+HBL 10S</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20118830</t>
+  </si>
+  <si>
+    <t>CHRM DN SRH+HRBL 16S</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20132816</t>
-  </si>
-  <si>
-    <t>FITTI PANTS 24'S XXL</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20136043</t>
-  </si>
-  <si>
-    <t>FITTI PNTS 40S/SMALL</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20134078</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX M</t>
-  </si>
-  <si>
-    <t>20134079</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX L</t>
-  </si>
-  <si>
-    <t>20134080</t>
-  </si>
-  <si>
-    <t>IDM BXER PRIA MAX XL</t>
-  </si>
-  <si>
-    <t>20134081</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF M 2S</t>
-  </si>
-  <si>
-    <t>20134082</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF L 2S</t>
-  </si>
-  <si>
-    <t>20134083</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF XL2S</t>
-  </si>
-  <si>
-    <t>20136272</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/M</t>
-  </si>
-  <si>
-    <t>20136273</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/L</t>
-  </si>
-  <si>
-    <t>20136274</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMX HTM/XL</t>
-  </si>
-  <si>
-    <t>20139172</t>
-  </si>
-  <si>
-    <t>G2G VITA C MOIST 30G</t>
+    <t>20026897</t>
+  </si>
+  <si>
+    <t>TESSA FAC.TISSUE 260</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20141838</t>
+  </si>
+  <si>
+    <t>PEPSODENT SG FIFA 1S</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
+  </si>
+  <si>
+    <t>20134841</t>
+  </si>
+  <si>
+    <t>CUSSONS TELON PLS 60</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20088537</t>
-  </si>
-  <si>
-    <t>GRNR VIT.C SPF36-20</t>
-  </si>
-  <si>
-    <t>20090447</t>
-  </si>
-  <si>
-    <t>GRNR SRM CR SPF30-20</t>
-  </si>
-  <si>
-    <t>20139173</t>
-  </si>
-  <si>
-    <t>G2G FW P.VITA C 80G</t>
-  </si>
-  <si>
-    <t>20141637</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW FIFA 85G</t>
-  </si>
-  <si>
-    <t>20141638</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW FIFA 500</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20141446</t>
-  </si>
-  <si>
-    <t>LFBUOY BW FIFA 360G</t>
+    <t>20137313</t>
+  </si>
+  <si>
+    <t>HANSPLST ANTSP 40ML</t>
+  </si>
+  <si>
+    <t>20108002</t>
+  </si>
+  <si>
+    <t>DOREMI H&amp;B WASH 200</t>
+  </si>
+  <si>
+    <t>20108003</t>
+  </si>
+  <si>
+    <t>DOREMI COLG HJB 100</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20044015</t>
-  </si>
-  <si>
-    <t>DOVE NOUR. B/WSH 400</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20026897</t>
-  </si>
-  <si>
-    <t>TESSA FAC.TISSUE 260</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20141838</t>
-  </si>
-  <si>
-    <t>PEPSODENT SG FIFA 1S</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>20127770</t>
-  </si>
-  <si>
-    <t>KODOMO P/G STRAWB 80</t>
+    <t>20087862</t>
+  </si>
+  <si>
+    <t>IDM MNUM DRMON 330ML</t>
+  </si>
+  <si>
+    <t>PT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20134841</t>
-  </si>
-  <si>
-    <t>CUSSONS TELON PLS 60</t>
-  </si>
-  <si>
-    <t>20137313</t>
-  </si>
-  <si>
-    <t>HANSPLST ANTSP 40ML</t>
-  </si>
-  <si>
-    <t>20108002</t>
-  </si>
-  <si>
-    <t>DOREMI H&amp;B WASH 200</t>
-  </si>
-  <si>
-    <t>20138274</t>
-  </si>
-  <si>
-    <t>ZWTSAL KIDS GREEN280</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20138275</t>
-  </si>
-  <si>
-    <t>ZWITSAL KIDS PINK280</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20108003</t>
-  </si>
-  <si>
-    <t>DOREMI COLG HJB 100</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20019179</t>
-  </si>
-  <si>
-    <t>B/BRAND GOLD MALT140</t>
-  </si>
-  <si>
-    <t>20067201</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGO TPK 1L</t>
-  </si>
-  <si>
-    <t>20115157</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
+    <t>20037159</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 18X20</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
-  </si>
-  <si>
-    <t>20037159</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 18X20</t>
   </si>
 </sst>
 </file>
@@ -718,15 +634,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -806,15 +721,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -823,7 +738,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -831,19 +746,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -851,19 +766,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -880,41 +795,41 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -923,7 +838,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -931,10 +846,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -943,7 +858,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -951,10 +866,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -963,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -971,10 +886,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -983,7 +898,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -991,10 +906,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1003,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1011,42 +926,42 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1060,13 +975,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1080,21 +995,21 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1103,18 +1018,18 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1123,150 +1038,150 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,313 +1195,53 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="1" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2B.xlsx
+++ b/E/EG2B.xlsx
@@ -11,141 +11,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
   <si>
     <t/>
   </si>
   <si>
+    <t>20071123</t>
+  </si>
+  <si>
+    <t>IDM JAS HUJAN SETLN</t>
+  </si>
+  <si>
+    <t>EG2B</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20090847</t>
+  </si>
+  <si>
+    <t>CERTAINTY POPOK 8S/M</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20090848</t>
+  </si>
+  <si>
+    <t>CERTAINTY POPOK 7S/L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20134081</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF M 2S</t>
+  </si>
+  <si>
+    <t>20134082</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF L 2S</t>
+  </si>
+  <si>
+    <t>20134083</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF XL2S</t>
+  </si>
+  <si>
+    <t>20134078</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX M</t>
+  </si>
+  <si>
+    <t>20134079</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX L</t>
+  </si>
+  <si>
+    <t>20134080</t>
+  </si>
+  <si>
+    <t>IDM BXER PRIA MAX XL</t>
+  </si>
+  <si>
+    <t>20136272</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/M</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20136273</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/L</t>
+  </si>
+  <si>
+    <t>20136274</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMX HTM/XL</t>
+  </si>
+  <si>
+    <t>20141637</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW FIFA 85G</t>
+  </si>
+  <si>
+    <t>20141446</t>
+  </si>
+  <si>
+    <t>LFBUOY BW FIFA 360G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141638</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW FIFA 500</t>
+  </si>
+  <si>
     <t>20128374</t>
   </si>
   <si>
     <t>LFEBUOY REF LIME 650</t>
   </si>
   <si>
-    <t>EG2B</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20134081</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF M 2S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20134082</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF L 2S</t>
-  </si>
-  <si>
-    <t>20134083</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF XL2S</t>
-  </si>
-  <si>
-    <t>20134078</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX M</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20134079</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX L</t>
-  </si>
-  <si>
-    <t>20134080</t>
-  </si>
-  <si>
-    <t>IDM BXER PRIA MAX XL</t>
-  </si>
-  <si>
-    <t>20136272</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/M</t>
-  </si>
-  <si>
-    <t>20136273</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/L</t>
-  </si>
-  <si>
-    <t>20136274</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMX HTM/XL</t>
-  </si>
-  <si>
-    <t>20141638</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW FIFA 500</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20141446</t>
-  </si>
-  <si>
-    <t>LFBUOY BW FIFA 360G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141637</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW FIFA 85G</t>
-  </si>
-  <si>
-    <t>20130843</t>
-  </si>
-  <si>
-    <t>CHARM DN SRH+HBL 10S</t>
+    <t>20028002</t>
+  </si>
+  <si>
+    <t>LFEBUOY SHP S&amp;SH 340</t>
   </si>
   <si>
     <t>PT,(E-4B)</t>
   </si>
   <si>
-    <t>20118830</t>
-  </si>
-  <si>
-    <t>CHRM DN SRH+HRBL 16S</t>
+    <t>20138900</t>
+  </si>
+  <si>
+    <t>SNSLK SHP AD</t>
+  </si>
+  <si>
+    <t>20140791</t>
+  </si>
+  <si>
+    <t>DOVE BIOTIN SHP 150</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20026897</t>
-  </si>
-  <si>
-    <t>TESSA FAC.TISSUE 260</t>
+    <t>20026207</t>
+  </si>
+  <si>
+    <t>CIPTADENT MX.COM 190</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>RT,(E-3B)</t>
   </si>
   <si>
     <t>20141838</t>
@@ -154,64 +190,40 @@
     <t>PEPSODENT SG FIFA 1S</t>
   </si>
   <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>20134841</t>
-  </si>
-  <si>
-    <t>CUSSONS TELON PLS 60</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137313</t>
-  </si>
-  <si>
-    <t>HANSPLST ANTSP 40ML</t>
-  </si>
-  <si>
-    <t>20108002</t>
-  </si>
-  <si>
-    <t>DOREMI H&amp;B WASH 200</t>
-  </si>
-  <si>
-    <t>20108003</t>
-  </si>
-  <si>
-    <t>DOREMI COLG HJB 100</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
-    <t>20087862</t>
-  </si>
-  <si>
-    <t>IDM MNUM DRMON 330ML</t>
-  </si>
-  <si>
-    <t>PT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20140882</t>
-  </si>
-  <si>
-    <t>LAYS WAVY SAPI 105G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>20136584</t>
+  </si>
+  <si>
+    <t>HMLAYA DS TRM.SRM 15</t>
+  </si>
+  <si>
+    <t>20139313</t>
+  </si>
+  <si>
+    <t>HMLY PRFY N/C SM 30</t>
+  </si>
+  <si>
+    <t>TG,(E-3B)</t>
+  </si>
+  <si>
+    <t>20139950</t>
+  </si>
+  <si>
+    <t>HMLY TURMERIC CSM 30</t>
+  </si>
+  <si>
+    <t>20136390</t>
+  </si>
+  <si>
+    <t>VSLNE LOT DW RDNC100</t>
+  </si>
+  <si>
+    <t>20136394</t>
+  </si>
+  <si>
+    <t>VSLNE LOT OVR RDN100</t>
   </si>
 </sst>
 </file>
@@ -604,14 +616,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -648,30 +660,30 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -685,53 +697,53 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -745,13 +757,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -765,13 +777,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -785,13 +797,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -805,13 +817,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -825,33 +837,33 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -865,273 +877,333 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>66</v>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
